--- a/Datos Experimentales/Data 24024.xlsx
+++ b/Datos Experimentales/Data 24024.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72544A3-4BA4-4A67-B90C-AD9B52B35AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
     <sheet name="Antecedentes" sheetId="2" r:id="rId2"/>
@@ -18,6 +28,7 @@
     <sheet name="Manual Densidades" sheetId="13" r:id="rId13"/>
     <sheet name="Winegrid densidad" sheetId="14" r:id="rId14"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1047,11 +1058,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1080,14 +1088,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1412,10 +1429,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B117"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1423,7 +1441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1431,7 +1449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1439,7 +1457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1447,7 +1465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1455,7 +1473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1463,7 +1481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1471,7 +1489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1479,7 +1497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1487,7 +1505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1495,7 +1513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1503,7 +1521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1511,7 +1529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1519,7 +1537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1527,7 +1545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1535,7 +1553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1543,7 +1561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1551,7 +1569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1559,7 +1577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1567,7 +1585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1575,7 +1593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1583,7 +1601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1591,7 +1609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1599,7 +1617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1607,7 +1625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1615,7 +1633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1623,7 +1641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1631,7 +1649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1639,7 +1657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1647,7 +1665,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1655,7 +1673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1663,7 +1681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1671,7 +1689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1679,7 +1697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1687,7 +1705,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1695,7 +1713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1703,7 +1721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1711,7 +1729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1719,7 +1737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1727,7 +1745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1735,7 +1753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1743,7 +1761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1751,7 +1769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1759,7 +1777,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1767,7 +1785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1775,7 +1793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1783,7 +1801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1791,7 +1809,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1799,7 +1817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1807,7 +1825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1815,7 +1833,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1823,7 +1841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1831,7 +1849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1839,7 +1857,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1847,7 +1865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1855,7 +1873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1863,7 +1881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1871,7 +1889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1879,7 +1897,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1887,7 +1905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1895,7 +1913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1903,7 +1921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1911,7 +1929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1919,7 +1937,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1927,7 +1945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1935,7 +1953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1943,7 +1961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1951,7 +1969,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1959,7 +1977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -1967,7 +1985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -1975,7 +1993,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -1983,7 +2001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -1991,7 +2009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -1999,7 +2017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2007,7 +2025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -2015,7 +2033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -2023,7 +2041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -2031,7 +2049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -2039,7 +2057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -2047,7 +2065,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>90</v>
       </c>
@@ -2055,7 +2073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -2063,7 +2081,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -2071,7 +2089,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2079,7 +2097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2087,7 +2105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2095,7 +2113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2103,7 +2121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2111,7 +2129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2119,7 +2137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -2127,7 +2145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -2135,7 +2153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -2143,7 +2161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -2151,7 +2169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -2159,7 +2177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -2167,7 +2185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>106</v>
       </c>
@@ -2175,7 +2193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -2183,7 +2201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -2191,7 +2209,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2199,7 +2217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2207,7 +2225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2215,7 +2233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2223,7 +2241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2231,7 +2249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2239,7 +2257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -2247,7 +2265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -2255,7 +2273,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -2263,7 +2281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -2271,7 +2289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -2279,7 +2297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>121</v>
       </c>
@@ -2287,7 +2305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>122</v>
       </c>
@@ -2295,7 +2313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>123</v>
       </c>
@@ -2303,7 +2321,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>124</v>
       </c>
@@ -2311,7 +2329,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>126</v>
       </c>
@@ -2319,7 +2337,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -2327,7 +2345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>128</v>
       </c>
@@ -2335,7 +2353,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>129</v>
       </c>
@@ -2343,7 +2361,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -2352,27 +2370,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B117"/>
+    <ignoredError sqref="A1:B117" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>281</v>
       </c>
@@ -2393,17 +2415,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>286</v>
       </c>
@@ -2414,7 +2438,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>289</v>
       </c>
@@ -2425,40 +2449,40 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>290</v>
       </c>
       <c r="B3">
-        <v>0.4736111111111111</v>
+        <v>0.47361111111111109</v>
       </c>
       <c r="C3">
         <v>17</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>291</v>
       </c>
       <c r="B4">
-        <v>0.7236111111111111</v>
+        <v>0.72361111111111109</v>
       </c>
       <c r="C4">
         <v>16.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>292</v>
       </c>
       <c r="B5">
-        <v>0.9736111111111111</v>
+        <v>0.97361111111111109</v>
       </c>
       <c r="C5">
         <v>17.5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>293</v>
       </c>
@@ -2469,7 +2493,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>294</v>
       </c>
@@ -2480,7 +2504,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>295</v>
       </c>
@@ -2491,7 +2515,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>296</v>
       </c>
@@ -2502,7 +2526,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>297</v>
       </c>
@@ -2513,7 +2537,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>298</v>
       </c>
@@ -2524,7 +2548,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>299</v>
       </c>
@@ -2535,7 +2559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>300</v>
       </c>
@@ -2546,7 +2570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>301</v>
       </c>
@@ -2557,7 +2581,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>302</v>
       </c>
@@ -2568,7 +2592,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>303</v>
       </c>
@@ -2579,7 +2603,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>304</v>
       </c>
@@ -2590,271 +2614,271 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>305</v>
       </c>
       <c r="B18">
-        <v>4.223611111111111</v>
+        <v>4.2236111111111114</v>
       </c>
       <c r="C18">
         <v>16.5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>306</v>
       </c>
       <c r="B19">
-        <v>4.473611111111111</v>
+        <v>4.4736111111111114</v>
       </c>
       <c r="C19">
         <v>17.5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>307</v>
       </c>
       <c r="B20">
-        <v>4.723611111111111</v>
+        <v>4.7236111111111114</v>
       </c>
       <c r="C20">
         <v>18</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>308</v>
       </c>
       <c r="B21">
-        <v>4.973611111111111</v>
+        <v>4.9736111111111114</v>
       </c>
       <c r="C21">
         <v>16</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>309</v>
       </c>
       <c r="B22">
-        <v>5.223611111111111</v>
+        <v>5.2236111111111114</v>
       </c>
       <c r="C22">
         <v>15.9</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>310</v>
       </c>
       <c r="B23">
-        <v>5.473611111111111</v>
+        <v>5.4736111111111114</v>
       </c>
       <c r="C23">
         <v>15.8</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>311</v>
       </c>
       <c r="B24">
-        <v>5.723611111111111</v>
+        <v>5.7236111111111114</v>
       </c>
       <c r="C24">
         <v>19</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>312</v>
       </c>
       <c r="B25">
-        <v>5.973611111111111</v>
+        <v>5.9736111111111114</v>
       </c>
       <c r="C25">
         <v>16</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>313</v>
       </c>
       <c r="B26">
-        <v>6.223611111111111</v>
+        <v>6.2236111111111114</v>
       </c>
       <c r="C26">
         <v>16.5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>314</v>
       </c>
       <c r="B27">
-        <v>6.473611111111111</v>
+        <v>6.4736111111111114</v>
       </c>
       <c r="C27">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>16.399999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>315</v>
       </c>
       <c r="B28">
-        <v>6.723611111111111</v>
+        <v>6.7236111111111114</v>
       </c>
       <c r="C28">
         <v>16.5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>316</v>
       </c>
       <c r="B29">
-        <v>6.973611111111111</v>
+        <v>6.9736111111111114</v>
       </c>
       <c r="C29">
         <v>16</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>317</v>
       </c>
       <c r="B30">
-        <v>7.223611111111111</v>
+        <v>7.2236111111111114</v>
       </c>
       <c r="C30">
         <v>16.3</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>318</v>
       </c>
       <c r="B31">
-        <v>7.473611111111111</v>
+        <v>7.4736111111111114</v>
       </c>
       <c r="C31">
         <v>16.5</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>319</v>
       </c>
       <c r="B32">
-        <v>7.723611111111111</v>
+        <v>7.7236111111111114</v>
       </c>
       <c r="C32">
-        <v>17.1</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>320</v>
       </c>
       <c r="B33">
-        <v>7.973611111111111</v>
+        <v>7.9736111111111114</v>
       </c>
       <c r="C33">
         <v>17.3</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>321</v>
       </c>
       <c r="B34">
-        <v>8.223611111111111</v>
+        <v>8.2236111111111114</v>
       </c>
       <c r="C34">
         <v>16.5</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>322</v>
       </c>
       <c r="B35">
-        <v>8.473611111111111</v>
+        <v>8.4736111111111114</v>
       </c>
       <c r="C35">
         <v>16.2</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>323</v>
       </c>
       <c r="B36">
-        <v>8.723611111111111</v>
+        <v>8.7236111111111114</v>
       </c>
       <c r="C36">
         <v>17.2</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>324</v>
       </c>
       <c r="B37">
-        <v>8.973611111111111</v>
+        <v>8.9736111111111114</v>
       </c>
       <c r="C37">
         <v>17</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>325</v>
       </c>
       <c r="B38">
-        <v>9.223611111111111</v>
+        <v>9.2236111111111114</v>
       </c>
       <c r="C38">
         <v>16.7</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>326</v>
       </c>
       <c r="B39">
-        <v>9.473611111111111</v>
+        <v>9.4736111111111114</v>
       </c>
       <c r="C39">
         <v>17.2</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>327</v>
       </c>
       <c r="B40">
-        <v>9.723611111111111</v>
+        <v>9.7236111111111114</v>
       </c>
       <c r="C40">
         <v>16.2</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>328</v>
       </c>
       <c r="B41">
-        <v>9.973611111111111</v>
+        <v>9.9736111111111114</v>
       </c>
       <c r="C41">
         <v>17.3</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>329</v>
       </c>
@@ -2865,7 +2889,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>330</v>
       </c>
@@ -2876,7 +2900,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>331</v>
       </c>
@@ -2887,7 +2911,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>332</v>
       </c>
@@ -2895,10 +2919,10 @@
         <v>10.973611111111111</v>
       </c>
       <c r="C45">
-        <v>16.9</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>333</v>
       </c>
@@ -2909,7 +2933,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>334</v>
       </c>
@@ -2920,7 +2944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>335</v>
       </c>
@@ -2928,10 +2952,10 @@
         <v>11.723611111111111</v>
       </c>
       <c r="C48">
-        <v>16.1</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>336</v>
       </c>
@@ -2943,17 +2967,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C49"/>
+    <ignoredError sqref="A1:C49" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>286</v>
       </c>
@@ -2964,7 +2990,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>289</v>
       </c>
@@ -2975,40 +3001,40 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>290</v>
       </c>
       <c r="B3">
-        <v>0.4736111111111111</v>
+        <v>0.47361111111111109</v>
       </c>
       <c r="C3">
         <v>1085</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>291</v>
       </c>
       <c r="B4">
-        <v>0.7236111111111111</v>
+        <v>0.72361111111111109</v>
       </c>
       <c r="C4">
         <v>1085</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>292</v>
       </c>
       <c r="B5">
-        <v>0.9736111111111111</v>
+        <v>0.97361111111111109</v>
       </c>
       <c r="C5">
         <v>1084</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>293</v>
       </c>
@@ -3019,7 +3045,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>294</v>
       </c>
@@ -3030,7 +3056,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>295</v>
       </c>
@@ -3041,7 +3067,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>296</v>
       </c>
@@ -3052,7 +3078,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>297</v>
       </c>
@@ -3063,7 +3089,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>298</v>
       </c>
@@ -3074,7 +3100,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>299</v>
       </c>
@@ -3085,7 +3111,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>300</v>
       </c>
@@ -3096,7 +3122,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>301</v>
       </c>
@@ -3107,7 +3133,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>302</v>
       </c>
@@ -3118,7 +3144,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>303</v>
       </c>
@@ -3129,7 +3155,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>304</v>
       </c>
@@ -3140,271 +3166,271 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>305</v>
       </c>
       <c r="B18">
-        <v>4.223611111111111</v>
+        <v>4.2236111111111114</v>
       </c>
       <c r="C18">
         <v>1027</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>306</v>
       </c>
       <c r="B19">
-        <v>4.473611111111111</v>
+        <v>4.4736111111111114</v>
       </c>
       <c r="C19">
         <v>1022</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>307</v>
       </c>
       <c r="B20">
-        <v>4.723611111111111</v>
+        <v>4.7236111111111114</v>
       </c>
       <c r="C20">
         <v>1019</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>308</v>
       </c>
       <c r="B21">
-        <v>4.973611111111111</v>
+        <v>4.9736111111111114</v>
       </c>
       <c r="C21">
         <v>1017</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>309</v>
       </c>
       <c r="B22">
-        <v>5.223611111111111</v>
+        <v>5.2236111111111114</v>
       </c>
       <c r="C22">
         <v>1017</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>310</v>
       </c>
       <c r="B23">
-        <v>5.473611111111111</v>
+        <v>5.4736111111111114</v>
       </c>
       <c r="C23">
         <v>1014</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>311</v>
       </c>
       <c r="B24">
-        <v>5.723611111111111</v>
+        <v>5.7236111111111114</v>
       </c>
       <c r="C24">
         <v>1011</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>312</v>
       </c>
       <c r="B25">
-        <v>5.973611111111111</v>
+        <v>5.9736111111111114</v>
       </c>
       <c r="C25">
         <v>1009</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>313</v>
       </c>
       <c r="B26">
-        <v>6.223611111111111</v>
+        <v>6.2236111111111114</v>
       </c>
       <c r="C26">
         <v>1011</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>314</v>
       </c>
       <c r="B27">
-        <v>6.473611111111111</v>
+        <v>6.4736111111111114</v>
       </c>
       <c r="C27">
         <v>1008</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>315</v>
       </c>
       <c r="B28">
-        <v>6.723611111111111</v>
+        <v>6.7236111111111114</v>
       </c>
       <c r="C28">
         <v>1007</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>316</v>
       </c>
       <c r="B29">
-        <v>6.973611111111111</v>
+        <v>6.9736111111111114</v>
       </c>
       <c r="C29">
         <v>1006</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>317</v>
       </c>
       <c r="B30">
-        <v>7.223611111111111</v>
+        <v>7.2236111111111114</v>
       </c>
       <c r="C30">
         <v>1005</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>318</v>
       </c>
       <c r="B31">
-        <v>7.473611111111111</v>
+        <v>7.4736111111111114</v>
       </c>
       <c r="C31">
         <v>1003</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>319</v>
       </c>
       <c r="B32">
-        <v>7.723611111111111</v>
+        <v>7.7236111111111114</v>
       </c>
       <c r="C32">
         <v>1003</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>320</v>
       </c>
       <c r="B33">
-        <v>7.973611111111111</v>
+        <v>7.9736111111111114</v>
       </c>
       <c r="C33">
         <v>1002</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>321</v>
       </c>
       <c r="B34">
-        <v>8.223611111111111</v>
+        <v>8.2236111111111114</v>
       </c>
       <c r="C34">
         <v>1001</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>322</v>
       </c>
       <c r="B35">
-        <v>8.473611111111111</v>
+        <v>8.4736111111111114</v>
       </c>
       <c r="C35">
         <v>1001</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>323</v>
       </c>
       <c r="B36">
-        <v>8.723611111111111</v>
+        <v>8.7236111111111114</v>
       </c>
       <c r="C36">
         <v>1000</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>324</v>
       </c>
       <c r="B37">
-        <v>8.973611111111111</v>
+        <v>8.9736111111111114</v>
       </c>
       <c r="C37">
         <v>1000</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>325</v>
       </c>
       <c r="B38">
-        <v>9.223611111111111</v>
+        <v>9.2236111111111114</v>
       </c>
       <c r="C38">
         <v>999</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>326</v>
       </c>
       <c r="B39">
-        <v>9.473611111111111</v>
+        <v>9.4736111111111114</v>
       </c>
       <c r="C39">
         <v>997</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>327</v>
       </c>
       <c r="B40">
-        <v>9.723611111111111</v>
+        <v>9.7236111111111114</v>
       </c>
       <c r="C40">
         <v>996</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>328</v>
       </c>
       <c r="B41">
-        <v>9.973611111111111</v>
+        <v>9.9736111111111114</v>
       </c>
       <c r="C41">
         <v>996</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>329</v>
       </c>
@@ -3415,7 +3441,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>330</v>
       </c>
@@ -3426,7 +3452,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>331</v>
       </c>
@@ -3437,7 +3463,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>332</v>
       </c>
@@ -3448,7 +3474,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>333</v>
       </c>
@@ -3459,7 +3485,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>334</v>
       </c>
@@ -3470,7 +3496,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>335</v>
       </c>
@@ -3481,7 +3507,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>336</v>
       </c>
@@ -3493,17 +3519,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C49"/>
+    <ignoredError sqref="A1:C49" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>286</v>
       </c>
@@ -3527,17 +3555,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CZ2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3851,7 +3881,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9844</v>
       </c>
@@ -3886,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>45373.65138888889</v>
+        <v>45373.651388888888</v>
       </c>
       <c r="M2" t="s">
         <v>135</v>
@@ -3895,7 +3925,7 @@
         <v>136</v>
       </c>
       <c r="O2">
-        <v>45380.65138888889</v>
+        <v>45380.651388888888</v>
       </c>
       <c r="P2" t="s">
         <v>137</v>
@@ -4075,7 +4105,7 @@
         <v>0</v>
       </c>
       <c r="BZ2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="CA2">
         <v>0</v>
@@ -4117,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="CN2">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="CO2">
         <v>0</v>
@@ -4141,21 +4171,23 @@
         <v>0</v>
       </c>
       <c r="CV2">
-        <v>16.6</v>
+        <v>16.600000000000001</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CZ2"/>
+    <ignoredError sqref="A1:CZ2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4208,7 +4240,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9844</v>
       </c>
@@ -4237,7 +4269,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9844</v>
       </c>
@@ -4272,7 +4304,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9844</v>
       </c>
@@ -4301,7 +4333,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9844</v>
       </c>
@@ -4315,7 +4347,7 @@
         <v>187</v>
       </c>
       <c r="E5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="F5" t="s">
         <v>183</v>
@@ -4351,7 +4383,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9844</v>
       </c>
@@ -4365,7 +4397,7 @@
         <v>187</v>
       </c>
       <c r="E6">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="F6" t="s">
         <v>183</v>
@@ -4401,7 +4433,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9844</v>
       </c>
@@ -4436,7 +4468,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9844</v>
       </c>
@@ -4483,7 +4515,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9844</v>
       </c>
@@ -4512,7 +4544,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9844</v>
       </c>
@@ -4547,7 +4579,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9844</v>
       </c>
@@ -4582,7 +4614,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9844</v>
       </c>
@@ -4618,17 +4650,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4660,7 +4694,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9844</v>
       </c>
@@ -4692,7 +4726,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9844</v>
       </c>
@@ -4724,7 +4758,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9844</v>
       </c>
@@ -4757,27 +4791,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4809,7 +4847,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9844</v>
       </c>
@@ -4842,17 +4880,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError sqref="A1:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4869,7 +4909,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9844</v>
       </c>
@@ -4881,27 +4921,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError sqref="A1:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4951,7 +4995,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9844</v>
       </c>
@@ -4964,7 +5008,7 @@
       <c r="D2">
         <v>6819</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>45373.777395833335</v>
       </c>
       <c r="F2" t="s">
@@ -4995,13 +5039,13 @@
         <v>244</v>
       </c>
       <c r="O2">
-        <v>7.5735</v>
+        <v>7.5735000000000001</v>
       </c>
       <c r="P2" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9844</v>
       </c>
@@ -5014,7 +5058,7 @@
       <c r="D3">
         <v>6819</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>45373.777395833335</v>
       </c>
       <c r="F3" t="s">
@@ -5045,13 +5089,13 @@
         <v>244</v>
       </c>
       <c r="O3">
-        <v>3.435</v>
+        <v>3.4350000000000001</v>
       </c>
       <c r="P3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9844</v>
       </c>
@@ -5064,7 +5108,7 @@
       <c r="D4">
         <v>6819</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>45373.777395833335</v>
       </c>
       <c r="F4" t="s">
@@ -5101,7 +5145,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9844</v>
       </c>
@@ -5114,7 +5158,7 @@
       <c r="D5">
         <v>6819</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>45373.777395833335</v>
       </c>
       <c r="F5" t="s">
@@ -5151,7 +5195,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9844</v>
       </c>
@@ -5164,7 +5208,7 @@
       <c r="D6">
         <v>6819</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <v>45373.777395833335</v>
       </c>
       <c r="F6" t="s">
@@ -5201,7 +5245,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9844</v>
       </c>
@@ -5214,7 +5258,7 @@
       <c r="D7">
         <v>6819</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="1">
         <v>45373.777395833335</v>
       </c>
       <c r="F7" t="s">
@@ -5251,7 +5295,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9844</v>
       </c>
@@ -5264,7 +5308,7 @@
       <c r="D8">
         <v>6819</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="1">
         <v>45373.777395833335</v>
       </c>
       <c r="F8" t="s">
@@ -5301,7 +5345,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9844</v>
       </c>
@@ -5314,8 +5358,8 @@
       <c r="D9">
         <v>6885</v>
       </c>
-      <c r="E9">
-        <v>45376.65798611111</v>
+      <c r="E9" s="1">
+        <v>45373.657986111109</v>
       </c>
       <c r="F9" t="s">
         <v>134</v>
@@ -5345,13 +5389,13 @@
         <v>244</v>
       </c>
       <c r="O9">
-        <v>7.9254</v>
+        <v>7.9253999999999998</v>
       </c>
       <c r="P9" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9844</v>
       </c>
@@ -5364,8 +5408,8 @@
       <c r="D10">
         <v>6885</v>
       </c>
-      <c r="E10">
-        <v>45376.65798611111</v>
+      <c r="E10" s="1">
+        <v>45373.657986111109</v>
       </c>
       <c r="F10" t="s">
         <v>134</v>
@@ -5401,7 +5445,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9844</v>
       </c>
@@ -5414,8 +5458,8 @@
       <c r="D11">
         <v>6885</v>
       </c>
-      <c r="E11">
-        <v>45376.65798611111</v>
+      <c r="E11" s="1">
+        <v>45373.657986111109</v>
       </c>
       <c r="F11" t="s">
         <v>134</v>
@@ -5445,13 +5489,13 @@
         <v>244</v>
       </c>
       <c r="O11">
-        <v>20.4</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="P11" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9844</v>
       </c>
@@ -5464,8 +5508,8 @@
       <c r="D12">
         <v>6885</v>
       </c>
-      <c r="E12">
-        <v>45376.65798611111</v>
+      <c r="E12" s="1">
+        <v>45373.657986111109</v>
       </c>
       <c r="F12" t="s">
         <v>134</v>
@@ -5501,7 +5545,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9844</v>
       </c>
@@ -5514,8 +5558,8 @@
       <c r="D13">
         <v>6885</v>
       </c>
-      <c r="E13">
-        <v>45376.65798611111</v>
+      <c r="E13" s="1">
+        <v>45373.657986111109</v>
       </c>
       <c r="F13" t="s">
         <v>134</v>
@@ -5551,7 +5595,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9844</v>
       </c>
@@ -5564,8 +5608,8 @@
       <c r="D14">
         <v>6885</v>
       </c>
-      <c r="E14">
-        <v>45376.65798611111</v>
+      <c r="E14" s="1">
+        <v>45373.657986111109</v>
       </c>
       <c r="F14" t="s">
         <v>134</v>
@@ -5601,7 +5645,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9844</v>
       </c>
@@ -5614,8 +5658,8 @@
       <c r="D15">
         <v>6885</v>
       </c>
-      <c r="E15">
-        <v>45376.65798611111</v>
+      <c r="E15" s="1">
+        <v>45373.657986111109</v>
       </c>
       <c r="F15" t="s">
         <v>134</v>
@@ -5651,7 +5695,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9844</v>
       </c>
@@ -5664,8 +5708,8 @@
       <c r="D16">
         <v>7167</v>
       </c>
-      <c r="E16">
-        <v>45384.85320601852</v>
+      <c r="E16" s="1">
+        <v>45384.853206018517</v>
       </c>
       <c r="F16" t="s">
         <v>134</v>
@@ -5701,7 +5745,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9844</v>
       </c>
@@ -5714,7 +5758,7 @@
       <c r="D17">
         <v>7233</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>45386.858506944445</v>
       </c>
       <c r="F17" t="s">
@@ -5751,7 +5795,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9844</v>
       </c>
@@ -5764,8 +5808,8 @@
       <c r="D18">
         <v>7286</v>
       </c>
-      <c r="E18">
-        <v>45387.75222222222</v>
+      <c r="E18" s="1">
+        <v>45387.752222222218</v>
       </c>
       <c r="F18" t="s">
         <v>134</v>
@@ -5801,7 +5845,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9844</v>
       </c>
@@ -5814,8 +5858,8 @@
       <c r="D19">
         <v>7286</v>
       </c>
-      <c r="E19">
-        <v>45387.75222222222</v>
+      <c r="E19" s="1">
+        <v>45387.752222222218</v>
       </c>
       <c r="F19" t="s">
         <v>134</v>
@@ -5845,13 +5889,13 @@
         <v>244</v>
       </c>
       <c r="O19">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="P19" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9844</v>
       </c>
@@ -5864,8 +5908,8 @@
       <c r="D20">
         <v>7286</v>
       </c>
-      <c r="E20">
-        <v>45387.75222222222</v>
+      <c r="E20" s="1">
+        <v>45387.752222222218</v>
       </c>
       <c r="F20" t="s">
         <v>134</v>
@@ -5901,7 +5945,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9844</v>
       </c>
@@ -5914,8 +5958,8 @@
       <c r="D21">
         <v>7286</v>
       </c>
-      <c r="E21">
-        <v>45387.75222222222</v>
+      <c r="E21" s="1">
+        <v>45387.752222222218</v>
       </c>
       <c r="F21" t="s">
         <v>134</v>
@@ -5951,7 +5995,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9844</v>
       </c>
@@ -5964,8 +6008,8 @@
       <c r="D22">
         <v>7286</v>
       </c>
-      <c r="E22">
-        <v>45387.75222222222</v>
+      <c r="E22" s="1">
+        <v>45387.752222222218</v>
       </c>
       <c r="F22" t="s">
         <v>134</v>
@@ -6001,7 +6045,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9844</v>
       </c>
@@ -6014,8 +6058,8 @@
       <c r="D23">
         <v>7286</v>
       </c>
-      <c r="E23">
-        <v>45387.75222222222</v>
+      <c r="E23" s="1">
+        <v>45387.752222222218</v>
       </c>
       <c r="F23" t="s">
         <v>134</v>
@@ -6051,7 +6095,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9844</v>
       </c>
@@ -6064,8 +6108,8 @@
       <c r="D24">
         <v>7286</v>
       </c>
-      <c r="E24">
-        <v>45387.75222222222</v>
+      <c r="E24" s="1">
+        <v>45387.752222222218</v>
       </c>
       <c r="F24" t="s">
         <v>134</v>
@@ -6101,7 +6145,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9844</v>
       </c>
@@ -6114,8 +6158,8 @@
       <c r="D25">
         <v>7286</v>
       </c>
-      <c r="E25">
-        <v>45387.75222222222</v>
+      <c r="E25" s="1">
+        <v>45387.752222222218</v>
       </c>
       <c r="F25" t="s">
         <v>134</v>
@@ -6151,7 +6195,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9844</v>
       </c>
@@ -6164,8 +6208,8 @@
       <c r="D26">
         <v>7286</v>
       </c>
-      <c r="E26">
-        <v>45387.75222222222</v>
+      <c r="E26" s="1">
+        <v>45387.752222222218</v>
       </c>
       <c r="F26" t="s">
         <v>134</v>
@@ -6201,7 +6245,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9844</v>
       </c>
@@ -6214,8 +6258,8 @@
       <c r="D27">
         <v>7286</v>
       </c>
-      <c r="E27">
-        <v>45387.75222222222</v>
+      <c r="E27" s="1">
+        <v>45387.752222222218</v>
       </c>
       <c r="F27" t="s">
         <v>134</v>
@@ -6251,7 +6295,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9844</v>
       </c>
@@ -6264,7 +6308,7 @@
       <c r="D28">
         <v>7460</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>45392.817152777774</v>
       </c>
       <c r="F28" t="s">
@@ -6301,7 +6345,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9844</v>
       </c>
@@ -6314,7 +6358,7 @@
       <c r="D29">
         <v>7460</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>45392.817152777774</v>
       </c>
       <c r="F29" t="s">
@@ -6351,7 +6395,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9844</v>
       </c>
@@ -6364,7 +6408,7 @@
       <c r="D30">
         <v>7460</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>45392.817152777774</v>
       </c>
       <c r="F30" t="s">
@@ -6401,7 +6445,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9844</v>
       </c>
@@ -6414,7 +6458,7 @@
       <c r="D31">
         <v>7460</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="1">
         <v>45392.817152777774</v>
       </c>
       <c r="F31" t="s">
@@ -6451,7 +6495,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9844</v>
       </c>
@@ -6464,7 +6508,7 @@
       <c r="D32">
         <v>7460</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="1">
         <v>45392.817152777774</v>
       </c>
       <c r="F32" t="s">
@@ -6495,13 +6539,13 @@
         <v>244</v>
       </c>
       <c r="O32">
-        <v>0.079</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="P32" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9844</v>
       </c>
@@ -6514,7 +6558,7 @@
       <c r="D33">
         <v>7460</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="1">
         <v>45392.817152777774</v>
       </c>
       <c r="F33" t="s">
@@ -6551,7 +6595,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9844</v>
       </c>
@@ -6564,7 +6608,7 @@
       <c r="D34">
         <v>7460</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="1">
         <v>45392.817152777774</v>
       </c>
       <c r="F34" t="s">
@@ -6595,13 +6639,13 @@
         <v>244</v>
       </c>
       <c r="O34">
-        <v>0.079</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="P34" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9844</v>
       </c>
@@ -6614,7 +6658,7 @@
       <c r="D35">
         <v>7460</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="1">
         <v>45392.817152777774</v>
       </c>
       <c r="F35" t="s">
@@ -6651,7 +6695,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9844</v>
       </c>
@@ -6664,7 +6708,7 @@
       <c r="D36">
         <v>7460</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="1">
         <v>45392.817152777774</v>
       </c>
       <c r="F36" t="s">
@@ -6701,7 +6745,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>9844</v>
       </c>
@@ -6714,7 +6758,7 @@
       <c r="D37">
         <v>7460</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="1">
         <v>45392.817152777774</v>
       </c>
       <c r="F37" t="s">
@@ -6752,8 +6796,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P37"/>
+    <ignoredError sqref="A1:P8 A16:P37 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Datos Experimentales/Data 24024.xlsx
+++ b/Datos Experimentales/Data 24024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72544A3-4BA4-4A67-B90C-AD9B52B35AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1A9B9D-6D90-499B-B0D6-152505E876E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
@@ -1431,9 +1431,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B117"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1465,7 +1465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1481,7 +1481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1545,7 +1545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1625,7 +1625,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1681,7 +1681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1721,7 +1721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1833,7 +1833,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1921,7 +1921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -2041,7 +2041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -2065,7 +2065,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>90</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -2089,7 +2089,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>106</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -2201,7 +2201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>110</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -2289,7 +2289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>121</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>122</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>123</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>124</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>126</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>128</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>129</v>
       </c>
@@ -2361,7 +2361,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -2380,7 +2380,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -2392,9 +2392,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>281</v>
       </c>
@@ -2425,9 +2425,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>286</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>289</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>290</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>291</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>292</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>293</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>294</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>295</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>296</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>297</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>298</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>299</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>300</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>301</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>302</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>303</v>
       </c>
@@ -2603,7 +2603,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>304</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>305</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>306</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>307</v>
       </c>
@@ -2647,7 +2647,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>308</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>309</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>15.9</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>310</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>311</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>312</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>313</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>314</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>315</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>316</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>317</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>318</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>319</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>320</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>321</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>322</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>323</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>324</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>325</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>326</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>327</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>328</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>329</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>330</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>331</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>332</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>333</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>334</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>335</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>336</v>
       </c>
@@ -2977,9 +2977,12 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>286</v>
       </c>
@@ -2990,7 +2993,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>289</v>
       </c>
@@ -3001,7 +3004,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>290</v>
       </c>
@@ -3012,7 +3015,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>291</v>
       </c>
@@ -3023,7 +3026,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>292</v>
       </c>
@@ -3034,7 +3037,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>293</v>
       </c>
@@ -3045,7 +3048,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>294</v>
       </c>
@@ -3056,7 +3059,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>295</v>
       </c>
@@ -3067,7 +3070,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>296</v>
       </c>
@@ -3078,7 +3081,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>297</v>
       </c>
@@ -3089,7 +3092,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>298</v>
       </c>
@@ -3100,7 +3103,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>299</v>
       </c>
@@ -3111,7 +3114,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>300</v>
       </c>
@@ -3122,7 +3125,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>301</v>
       </c>
@@ -3133,7 +3136,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>302</v>
       </c>
@@ -3144,7 +3147,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>303</v>
       </c>
@@ -3155,7 +3158,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>304</v>
       </c>
@@ -3166,7 +3169,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>305</v>
       </c>
@@ -3177,7 +3180,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>306</v>
       </c>
@@ -3188,7 +3191,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>307</v>
       </c>
@@ -3199,7 +3202,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>308</v>
       </c>
@@ -3210,7 +3213,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>309</v>
       </c>
@@ -3221,7 +3224,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>310</v>
       </c>
@@ -3232,7 +3235,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>311</v>
       </c>
@@ -3243,7 +3246,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>312</v>
       </c>
@@ -3254,7 +3257,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>313</v>
       </c>
@@ -3265,7 +3268,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>314</v>
       </c>
@@ -3276,7 +3279,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>315</v>
       </c>
@@ -3287,7 +3290,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>316</v>
       </c>
@@ -3298,7 +3301,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>317</v>
       </c>
@@ -3309,7 +3312,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>318</v>
       </c>
@@ -3320,7 +3323,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>319</v>
       </c>
@@ -3331,7 +3334,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>320</v>
       </c>
@@ -3342,7 +3345,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>321</v>
       </c>
@@ -3353,7 +3356,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>322</v>
       </c>
@@ -3364,7 +3367,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>323</v>
       </c>
@@ -3375,7 +3378,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>324</v>
       </c>
@@ -3386,7 +3389,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>325</v>
       </c>
@@ -3397,7 +3400,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>326</v>
       </c>
@@ -3408,7 +3411,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>327</v>
       </c>
@@ -3419,7 +3422,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>328</v>
       </c>
@@ -3430,7 +3433,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>329</v>
       </c>
@@ -3441,7 +3444,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>330</v>
       </c>
@@ -3452,7 +3455,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>331</v>
       </c>
@@ -3463,7 +3466,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>332</v>
       </c>
@@ -3474,7 +3477,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>333</v>
       </c>
@@ -3485,7 +3488,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>334</v>
       </c>
@@ -3496,7 +3499,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>335</v>
       </c>
@@ -3507,7 +3510,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>336</v>
       </c>
@@ -3529,9 +3532,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>286</v>
       </c>
@@ -3565,9 +3568,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CZ2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:104" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -3881,7 +3884,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:104" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:104" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9844</v>
       </c>
@@ -4185,9 +4188,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4240,7 +4243,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9844</v>
       </c>
@@ -4269,7 +4272,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9844</v>
       </c>
@@ -4304,7 +4307,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9844</v>
       </c>
@@ -4333,7 +4336,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9844</v>
       </c>
@@ -4383,7 +4386,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9844</v>
       </c>
@@ -4418,7 +4421,7 @@
         <v>135</v>
       </c>
       <c r="L6">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="M6" t="s">
         <v>5</v>
@@ -4433,7 +4436,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9844</v>
       </c>
@@ -4468,7 +4471,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9844</v>
       </c>
@@ -4515,7 +4518,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9844</v>
       </c>
@@ -4544,7 +4547,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9844</v>
       </c>
@@ -4579,7 +4582,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9844</v>
       </c>
@@ -4614,7 +4617,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9844</v>
       </c>
@@ -4652,7 +4655,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:Q5 A9:Q12 A8:K8 M8:Q8 A7:Q7 A6:K6 M6:Q6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4660,9 +4663,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4694,7 +4697,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9844</v>
       </c>
@@ -4717,7 +4720,7 @@
         <v>213</v>
       </c>
       <c r="H2">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="I2">
         <v>45372</v>
@@ -4726,7 +4729,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9844</v>
       </c>
@@ -4758,7 +4761,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9844</v>
       </c>
@@ -4781,7 +4784,7 @@
         <v>215</v>
       </c>
       <c r="H4">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="I4">
         <v>45373</v>
@@ -4793,7 +4796,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 A3:J3 A2:G2 I2:J2 A4:G4 I4:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4801,7 +4804,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4813,9 +4816,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4847,7 +4850,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9844</v>
       </c>
@@ -4890,9 +4893,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4909,7 +4912,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9844</v>
       </c>
@@ -4931,7 +4934,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4943,9 +4946,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>162</v>
       </c>
@@ -4995,7 +4998,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9844</v>
       </c>
@@ -5045,7 +5048,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9844</v>
       </c>
@@ -5095,7 +5098,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9844</v>
       </c>
@@ -5145,7 +5148,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9844</v>
       </c>
@@ -5195,7 +5198,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9844</v>
       </c>
@@ -5245,7 +5248,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9844</v>
       </c>
@@ -5295,7 +5298,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9844</v>
       </c>
@@ -5345,7 +5348,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9844</v>
       </c>
@@ -5395,7 +5398,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9844</v>
       </c>
@@ -5445,7 +5448,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9844</v>
       </c>
@@ -5495,7 +5498,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9844</v>
       </c>
@@ -5545,7 +5548,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9844</v>
       </c>
@@ -5595,7 +5598,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9844</v>
       </c>
@@ -5645,7 +5648,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9844</v>
       </c>
@@ -5695,7 +5698,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9844</v>
       </c>
@@ -5745,7 +5748,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9844</v>
       </c>
@@ -5795,7 +5798,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9844</v>
       </c>
@@ -5845,7 +5848,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9844</v>
       </c>
@@ -5895,7 +5898,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9844</v>
       </c>
@@ -5945,7 +5948,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9844</v>
       </c>
@@ -5995,7 +5998,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9844</v>
       </c>
@@ -6045,7 +6048,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9844</v>
       </c>
@@ -6095,7 +6098,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9844</v>
       </c>
@@ -6145,7 +6148,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9844</v>
       </c>
@@ -6195,7 +6198,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9844</v>
       </c>
@@ -6245,7 +6248,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9844</v>
       </c>
@@ -6295,7 +6298,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9844</v>
       </c>
@@ -6345,7 +6348,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9844</v>
       </c>
@@ -6395,7 +6398,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9844</v>
       </c>
@@ -6445,7 +6448,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9844</v>
       </c>
@@ -6495,7 +6498,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9844</v>
       </c>
@@ -6545,7 +6548,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9844</v>
       </c>
@@ -6595,7 +6598,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9844</v>
       </c>
@@ -6645,7 +6648,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9844</v>
       </c>
@@ -6695,7 +6698,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9844</v>
       </c>
@@ -6745,7 +6748,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>9844</v>
       </c>
